--- a/diseases/d017/1995-1999.xlsx
+++ b/diseases/d017/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>11</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>4</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>4</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>6</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20167,9 +20020,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20791,9 +20641,6 @@
       <c r="O104" t="n">
         <v>6</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21184,9 +21031,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21953,9 +21797,6 @@
       <c r="O110" t="n">
         <v>2</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22346,9 +22187,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23115,9 +22953,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23508,9 +23343,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24277,9 +24109,6 @@
       <c r="O122" t="n">
         <v>2</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24670,9 +24499,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25439,9 +25265,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25832,9 +25655,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26601,9 +26421,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26994,9 +26811,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27763,9 +27577,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28156,9 +27967,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28925,9 +28733,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29318,9 +29123,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30087,9 +29889,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30480,9 +30279,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31249,9 +31045,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31642,9 +31435,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32411,9 +32201,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32804,9 +32591,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33573,9 +33357,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33966,9 +33747,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34504,9 +34282,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="S175" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35128,9 +34903,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35521,9 +35293,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36290,9 +36059,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36683,9 +36449,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37452,9 +37215,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37845,9 +37605,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38614,9 +38371,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39007,9 +38761,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39776,9 +39527,6 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40169,9 +39917,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40938,9 +40683,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41331,9 +41073,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42100,9 +41839,6 @@
       <c r="O214" t="n">
         <v>0</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42493,9 +42229,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43262,9 +42995,6 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43655,9 +43385,6 @@
       <c r="O222" t="n">
         <v>0</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44424,9 +44151,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44817,9 +44541,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45586,9 +45307,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45979,9 +45697,6 @@
       <c r="O234" t="n">
         <v>1</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46748,9 +46463,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47141,9 +46853,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47910,9 +47619,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48303,9 +48009,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48841,9 +48544,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49465,9 +49165,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -49858,9 +49555,6 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="S254" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -50627,9 +50321,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51020,9 +50711,6 @@
       <c r="O260" t="n">
         <v>0</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -51789,9 +51477,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="S264" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52182,9 +51867,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -52951,9 +52633,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="S270" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -53344,9 +53023,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="S272" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54113,9 +53789,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="S276" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -54506,9 +54179,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="S278" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55275,9 +54945,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="S282" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -55668,9 +55335,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="S284" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56437,9 +56101,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="S288" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -56830,9 +56491,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="S290" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -57599,9 +57257,6 @@
       <c r="O294" t="n">
         <v>1</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="S294" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -57992,9 +57647,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="S296" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -58761,9 +58413,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="S300" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -59154,9 +58803,6 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="S302" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -59923,9 +59569,6 @@
       <c r="O306" t="n">
         <v>0</v>
       </c>
-      <c r="Q306" t="n">
-        <v>0</v>
-      </c>
       <c r="S306" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -60316,9 +59959,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="S308" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -61085,9 +60725,6 @@
       <c r="O312" t="n">
         <v>1</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="S312" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -61478,9 +61115,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="S314" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -62246,9 +61880,6 @@
       </c>
       <c r="O318" t="n">
         <v>1</v>
-      </c>
-      <c r="Q318" t="n">
-        <v>0</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
